--- a/clients/Poojamani/AY 2026-27/document_checklist.xlsx
+++ b/clients/Poojamani/AY 2026-27/document_checklist.xlsx
@@ -85,7 +85,7 @@
     <t>Creditors List</t>
   </si>
   <si>
-    <t>Pending</t>
+    <t>Received</t>
   </si>
 </sst>
 </file>

--- a/clients/Poojamani/AY 2026-27/document_checklist.xlsx
+++ b/clients/Poojamani/AY 2026-27/document_checklist.xlsx
@@ -14,7 +14,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="415" uniqueCount="124">
+  <si>
+    <t>Category</t>
+  </si>
   <si>
     <t>Document Name</t>
   </si>
@@ -25,6 +28,48 @@
     <t>Remarks</t>
   </si>
   <si>
+    <t>Other Documents</t>
+  </si>
+  <si>
+    <t>Basic Books Data</t>
+  </si>
+  <si>
+    <t>Sales and Purchase Data</t>
+  </si>
+  <si>
+    <t>GST Data</t>
+  </si>
+  <si>
+    <t>TDS / TCS Data</t>
+  </si>
+  <si>
+    <t>Statutory Dues and 43B Data</t>
+  </si>
+  <si>
+    <t>Payroll / PF / ESI Data</t>
+  </si>
+  <si>
+    <t>Loans and Finance Data</t>
+  </si>
+  <si>
+    <t>Fixed Assets and Depreciation Data</t>
+  </si>
+  <si>
+    <t>Related Party Data</t>
+  </si>
+  <si>
+    <t>MSME Data</t>
+  </si>
+  <si>
+    <t>Stock and Quantitative Data</t>
+  </si>
+  <si>
+    <t>Other Tax and Reporting Data</t>
+  </si>
+  <si>
+    <t>Final Audit Review Data</t>
+  </si>
+  <si>
     <t>Bank Statements</t>
   </si>
   <si>
@@ -85,7 +130,262 @@
     <t>Creditors List</t>
   </si>
   <si>
+    <t>Trial_Balance</t>
+  </si>
+  <si>
+    <t>Ledger_Master</t>
+  </si>
+  <si>
+    <t>Ledger_Details</t>
+  </si>
+  <si>
+    <t>Opening_Balances</t>
+  </si>
+  <si>
+    <t>Financial_Statements</t>
+  </si>
+  <si>
+    <t>Profit_and_Loss</t>
+  </si>
+  <si>
+    <t>Balance_Sheet</t>
+  </si>
+  <si>
+    <t>Previous_Year_Financials</t>
+  </si>
+  <si>
+    <t>Books_Sales</t>
+  </si>
+  <si>
+    <t>Books_Purchases</t>
+  </si>
+  <si>
+    <t>Sales_Register</t>
+  </si>
+  <si>
+    <t>Purchase_Register</t>
+  </si>
+  <si>
+    <t>Customer_Master</t>
+  </si>
+  <si>
+    <t>Vendor_Master</t>
+  </si>
+  <si>
+    <t>GSTR1</t>
+  </si>
+  <si>
+    <t>GSTR3B</t>
+  </si>
+  <si>
+    <t>GSTR2A</t>
+  </si>
+  <si>
+    <t>GSTR2B</t>
+  </si>
+  <si>
+    <t>GST_Output_Ledger</t>
+  </si>
+  <si>
+    <t>GST_Input_Ledger</t>
+  </si>
+  <si>
+    <t>GST_Ledger</t>
+  </si>
+  <si>
+    <t>GST_ITC_Books</t>
+  </si>
+  <si>
+    <t>GST_Payments</t>
+  </si>
+  <si>
+    <t>GST_Return_Status</t>
+  </si>
+  <si>
+    <t>GSTIN_Master</t>
+  </si>
+  <si>
+    <t>Expense_Ledgers</t>
+  </si>
+  <si>
+    <t>TDS_Deducted</t>
+  </si>
+  <si>
+    <t>TDS_Payments</t>
+  </si>
+  <si>
+    <t>TDS_Returns</t>
+  </si>
+  <si>
+    <t>TDS_Ledger</t>
+  </si>
+  <si>
+    <t>TDS_Receivable_Ledger</t>
+  </si>
+  <si>
+    <t>Form_26Q</t>
+  </si>
+  <si>
+    <t>Form_24Q</t>
+  </si>
+  <si>
+    <t>Form_27Q</t>
+  </si>
+  <si>
+    <t>Form_27EQ</t>
+  </si>
+  <si>
+    <t>Form_26AS</t>
+  </si>
+  <si>
+    <t>AIS_TIS</t>
+  </si>
+  <si>
+    <t>Statutory_Dues</t>
+  </si>
+  <si>
+    <t>PF_ESI_Details</t>
+  </si>
+  <si>
+    <t>PF_Returns</t>
+  </si>
+  <si>
+    <t>ESI_Returns</t>
+  </si>
+  <si>
+    <t>Professional_Tax_Returns</t>
+  </si>
+  <si>
+    <t>Bonus_Details</t>
+  </si>
+  <si>
+    <t>Leave_Encashment_Details</t>
+  </si>
+  <si>
+    <t>Interest_To_Banks_FI</t>
+  </si>
+  <si>
+    <t>Loan_Interest_Details</t>
+  </si>
+  <si>
+    <t>Payment_Register</t>
+  </si>
+  <si>
+    <t>Bank_Book</t>
+  </si>
+  <si>
+    <t>Salary_Register</t>
+  </si>
+  <si>
+    <t>PF_Challans</t>
+  </si>
+  <si>
+    <t>ESI_Challans</t>
+  </si>
+  <si>
+    <t>Loan_Details</t>
+  </si>
+  <si>
+    <t>Party_Master</t>
+  </si>
+  <si>
+    <t>Cash_Book</t>
+  </si>
+  <si>
+    <t>Receipt_Register</t>
+  </si>
+  <si>
+    <t>Fixed_Asset_Register</t>
+  </si>
+  <si>
+    <t>Additions</t>
+  </si>
+  <si>
+    <t>Deletions</t>
+  </si>
+  <si>
+    <t>Depreciation_As_Per_Books</t>
+  </si>
+  <si>
+    <t>Depreciation_As_Per_IT</t>
+  </si>
+  <si>
+    <t>Related_Party_Master</t>
+  </si>
+  <si>
+    <t>Partner_Director_Details</t>
+  </si>
+  <si>
+    <t>MSME_Vendor_List</t>
+  </si>
+  <si>
+    <t>Creditor_Ageing</t>
+  </si>
+  <si>
+    <t>Outstanding_Payables</t>
+  </si>
+  <si>
+    <t>Stock_Register</t>
+  </si>
+  <si>
+    <t>Production_Register</t>
+  </si>
+  <si>
+    <t>Opening_Stock</t>
+  </si>
+  <si>
+    <t>Closing_Stock</t>
+  </si>
+  <si>
+    <t>Physical_Verification_Report</t>
+  </si>
+  <si>
+    <t>Tax_Demand_Refund_Details</t>
+  </si>
+  <si>
+    <t>GST_Orders</t>
+  </si>
+  <si>
+    <t>VAT_Orders</t>
+  </si>
+  <si>
+    <t>Professional_Tax_Orders</t>
+  </si>
+  <si>
+    <t>Other_Tax_Orders</t>
+  </si>
+  <si>
+    <t>Appeal_Details</t>
+  </si>
+  <si>
+    <t>SFT_Transactions</t>
+  </si>
+  <si>
+    <t>Form_61_61A_61B_Status</t>
+  </si>
+  <si>
+    <t>High_Value_Transactions</t>
+  </si>
+  <si>
+    <t>Exception_Report</t>
+  </si>
+  <si>
+    <t>Management_Reply</t>
+  </si>
+  <si>
+    <t>Auditor_Remarks</t>
+  </si>
+  <si>
+    <t>Final_Adjustments</t>
+  </si>
+  <si>
+    <t>Tax_Report_Linkage</t>
+  </si>
+  <si>
     <t>Received</t>
+  </si>
+  <si>
+    <t>Pending</t>
   </si>
 </sst>
 </file>
@@ -417,10 +717,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C21"/>
+  <dimension ref="A1:D138"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:4">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -430,165 +730,1515 @@
       <c r="C1" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:3">
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
       <c r="A2" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B2" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
+        <v>18</v>
+      </c>
+      <c r="C2" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
       <c r="A3" t="s">
         <v>4</v>
       </c>
       <c r="B3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
+        <v>19</v>
+      </c>
+      <c r="C3" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
       <c r="A4" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B4" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
+        <v>20</v>
+      </c>
+      <c r="C4" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
       <c r="A5" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
+        <v>21</v>
+      </c>
+      <c r="C5" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
       <c r="A6" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
+        <v>22</v>
+      </c>
+      <c r="C6" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
       <c r="A7" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="B7" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="8" spans="1:3">
+      <c r="C7" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
       <c r="A8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B8" t="s">
+        <v>24</v>
+      </c>
+      <c r="C8" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" t="s">
+        <v>4</v>
+      </c>
+      <c r="B9" t="s">
+        <v>25</v>
+      </c>
+      <c r="C9" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B10" t="s">
+        <v>26</v>
+      </c>
+      <c r="C10" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11" t="s">
+        <v>4</v>
+      </c>
+      <c r="B11" t="s">
+        <v>27</v>
+      </c>
+      <c r="C11" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12" t="s">
+        <v>4</v>
+      </c>
+      <c r="B12" t="s">
+        <v>28</v>
+      </c>
+      <c r="C12" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13" t="s">
+        <v>4</v>
+      </c>
+      <c r="B13" t="s">
+        <v>29</v>
+      </c>
+      <c r="C13" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14" t="s">
+        <v>4</v>
+      </c>
+      <c r="B14" t="s">
+        <v>30</v>
+      </c>
+      <c r="C14" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4">
+      <c r="A15" t="s">
+        <v>4</v>
+      </c>
+      <c r="B15" t="s">
+        <v>31</v>
+      </c>
+      <c r="C15" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4">
+      <c r="A16" t="s">
+        <v>4</v>
+      </c>
+      <c r="B16" t="s">
+        <v>32</v>
+      </c>
+      <c r="C16" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17" t="s">
+        <v>4</v>
+      </c>
+      <c r="B17" t="s">
+        <v>33</v>
+      </c>
+      <c r="C17" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" t="s">
+        <v>4</v>
+      </c>
+      <c r="B18" t="s">
+        <v>34</v>
+      </c>
+      <c r="C18" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19" t="s">
+        <v>4</v>
+      </c>
+      <c r="B19" t="s">
+        <v>35</v>
+      </c>
+      <c r="C19" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20" t="s">
+        <v>4</v>
+      </c>
+      <c r="B20" t="s">
+        <v>36</v>
+      </c>
+      <c r="C20" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21" t="s">
+        <v>4</v>
+      </c>
+      <c r="B21" t="s">
+        <v>37</v>
+      </c>
+      <c r="C21" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3">
+      <c r="A22" t="s">
+        <v>5</v>
+      </c>
+      <c r="B22" t="s">
+        <v>38</v>
+      </c>
+      <c r="C22" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3">
+      <c r="A23" t="s">
+        <v>5</v>
+      </c>
+      <c r="B23" t="s">
+        <v>39</v>
+      </c>
+      <c r="C23" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3">
+      <c r="A24" t="s">
+        <v>5</v>
+      </c>
+      <c r="B24" t="s">
+        <v>40</v>
+      </c>
+      <c r="C24" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3">
+      <c r="A25" t="s">
+        <v>5</v>
+      </c>
+      <c r="B25" t="s">
+        <v>41</v>
+      </c>
+      <c r="C25" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3">
+      <c r="A26" t="s">
+        <v>5</v>
+      </c>
+      <c r="B26" t="s">
+        <v>42</v>
+      </c>
+      <c r="C26" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3">
+      <c r="A27" t="s">
+        <v>5</v>
+      </c>
+      <c r="B27" t="s">
+        <v>43</v>
+      </c>
+      <c r="C27" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3">
+      <c r="A28" t="s">
+        <v>5</v>
+      </c>
+      <c r="B28" t="s">
+        <v>44</v>
+      </c>
+      <c r="C28" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3">
+      <c r="A29" t="s">
+        <v>5</v>
+      </c>
+      <c r="B29" t="s">
+        <v>45</v>
+      </c>
+      <c r="C29" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3">
+      <c r="A30" t="s">
+        <v>6</v>
+      </c>
+      <c r="B30" t="s">
+        <v>46</v>
+      </c>
+      <c r="C30" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3">
+      <c r="A31" t="s">
+        <v>6</v>
+      </c>
+      <c r="B31" t="s">
+        <v>47</v>
+      </c>
+      <c r="C31" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3">
+      <c r="A32" t="s">
+        <v>6</v>
+      </c>
+      <c r="B32" t="s">
+        <v>48</v>
+      </c>
+      <c r="C32" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3">
+      <c r="A33" t="s">
+        <v>6</v>
+      </c>
+      <c r="B33" t="s">
+        <v>49</v>
+      </c>
+      <c r="C33" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3">
+      <c r="A34" t="s">
+        <v>6</v>
+      </c>
+      <c r="B34" t="s">
+        <v>50</v>
+      </c>
+      <c r="C34" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3">
+      <c r="A35" t="s">
+        <v>6</v>
+      </c>
+      <c r="B35" t="s">
+        <v>51</v>
+      </c>
+      <c r="C35" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3">
+      <c r="A36" t="s">
+        <v>7</v>
+      </c>
+      <c r="B36" t="s">
+        <v>52</v>
+      </c>
+      <c r="C36" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3">
+      <c r="A37" t="s">
+        <v>7</v>
+      </c>
+      <c r="B37" t="s">
+        <v>53</v>
+      </c>
+      <c r="C37" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3">
+      <c r="A38" t="s">
+        <v>7</v>
+      </c>
+      <c r="B38" t="s">
+        <v>54</v>
+      </c>
+      <c r="C38" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3">
+      <c r="A39" t="s">
+        <v>7</v>
+      </c>
+      <c r="B39" t="s">
+        <v>55</v>
+      </c>
+      <c r="C39" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3">
+      <c r="A40" t="s">
+        <v>7</v>
+      </c>
+      <c r="B40" t="s">
+        <v>56</v>
+      </c>
+      <c r="C40" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3">
+      <c r="A41" t="s">
+        <v>7</v>
+      </c>
+      <c r="B41" t="s">
+        <v>57</v>
+      </c>
+      <c r="C41" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3">
+      <c r="A42" t="s">
+        <v>7</v>
+      </c>
+      <c r="B42" t="s">
+        <v>58</v>
+      </c>
+      <c r="C42" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3">
+      <c r="A43" t="s">
+        <v>7</v>
+      </c>
+      <c r="B43" t="s">
+        <v>59</v>
+      </c>
+      <c r="C43" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3">
+      <c r="A44" t="s">
+        <v>7</v>
+      </c>
+      <c r="B44" t="s">
+        <v>60</v>
+      </c>
+      <c r="C44" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3">
+      <c r="A45" t="s">
+        <v>7</v>
+      </c>
+      <c r="B45" t="s">
+        <v>61</v>
+      </c>
+      <c r="C45" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3">
+      <c r="A46" t="s">
+        <v>7</v>
+      </c>
+      <c r="B46" t="s">
+        <v>62</v>
+      </c>
+      <c r="C46" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3">
+      <c r="A47" t="s">
+        <v>8</v>
+      </c>
+      <c r="B47" t="s">
+        <v>63</v>
+      </c>
+      <c r="C47" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3">
+      <c r="A48" t="s">
+        <v>8</v>
+      </c>
+      <c r="B48" t="s">
+        <v>64</v>
+      </c>
+      <c r="C48" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3">
+      <c r="A49" t="s">
+        <v>8</v>
+      </c>
+      <c r="B49" t="s">
+        <v>65</v>
+      </c>
+      <c r="C49" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3">
+      <c r="A50" t="s">
+        <v>8</v>
+      </c>
+      <c r="B50" t="s">
+        <v>66</v>
+      </c>
+      <c r="C50" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3">
+      <c r="A51" t="s">
+        <v>8</v>
+      </c>
+      <c r="B51" t="s">
+        <v>67</v>
+      </c>
+      <c r="C51" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3">
+      <c r="A52" t="s">
+        <v>8</v>
+      </c>
+      <c r="B52" t="s">
+        <v>68</v>
+      </c>
+      <c r="C52" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3">
+      <c r="A53" t="s">
+        <v>8</v>
+      </c>
+      <c r="B53" t="s">
+        <v>69</v>
+      </c>
+      <c r="C53" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3">
+      <c r="A54" t="s">
+        <v>8</v>
+      </c>
+      <c r="B54" t="s">
+        <v>70</v>
+      </c>
+      <c r="C54" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3">
+      <c r="A55" t="s">
+        <v>8</v>
+      </c>
+      <c r="B55" t="s">
+        <v>71</v>
+      </c>
+      <c r="C55" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3">
+      <c r="A56" t="s">
+        <v>8</v>
+      </c>
+      <c r="B56" t="s">
+        <v>72</v>
+      </c>
+      <c r="C56" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3">
+      <c r="A57" t="s">
+        <v>8</v>
+      </c>
+      <c r="B57" t="s">
+        <v>73</v>
+      </c>
+      <c r="C57" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3">
+      <c r="A58" t="s">
+        <v>8</v>
+      </c>
+      <c r="B58" t="s">
+        <v>74</v>
+      </c>
+      <c r="C58" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3">
+      <c r="A59" t="s">
         <v>9</v>
       </c>
-      <c r="B8" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3">
-      <c r="A9" t="s">
+      <c r="B59" t="s">
+        <v>75</v>
+      </c>
+      <c r="C59" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3">
+      <c r="A60" t="s">
+        <v>9</v>
+      </c>
+      <c r="B60" t="s">
+        <v>61</v>
+      </c>
+      <c r="C60" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3">
+      <c r="A61" t="s">
+        <v>9</v>
+      </c>
+      <c r="B61" t="s">
+        <v>58</v>
+      </c>
+      <c r="C61" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3">
+      <c r="A62" t="s">
+        <v>9</v>
+      </c>
+      <c r="B62" t="s">
+        <v>60</v>
+      </c>
+      <c r="C62" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3">
+      <c r="A63" t="s">
+        <v>9</v>
+      </c>
+      <c r="B63" t="s">
+        <v>53</v>
+      </c>
+      <c r="C63" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3">
+      <c r="A64" t="s">
+        <v>9</v>
+      </c>
+      <c r="B64" t="s">
+        <v>67</v>
+      </c>
+      <c r="C64" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3">
+      <c r="A65" t="s">
+        <v>9</v>
+      </c>
+      <c r="B65" t="s">
+        <v>64</v>
+      </c>
+      <c r="C65" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3">
+      <c r="A66" t="s">
+        <v>9</v>
+      </c>
+      <c r="B66" t="s">
+        <v>65</v>
+      </c>
+      <c r="C66" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3">
+      <c r="A67" t="s">
+        <v>9</v>
+      </c>
+      <c r="B67" t="s">
+        <v>66</v>
+      </c>
+      <c r="C67" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3">
+      <c r="A68" t="s">
+        <v>9</v>
+      </c>
+      <c r="B68" t="s">
+        <v>76</v>
+      </c>
+      <c r="C68" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3">
+      <c r="A69" t="s">
+        <v>9</v>
+      </c>
+      <c r="B69" t="s">
+        <v>77</v>
+      </c>
+      <c r="C69" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3">
+      <c r="A70" t="s">
+        <v>9</v>
+      </c>
+      <c r="B70" t="s">
+        <v>78</v>
+      </c>
+      <c r="C70" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3">
+      <c r="A71" t="s">
+        <v>9</v>
+      </c>
+      <c r="B71" t="s">
+        <v>79</v>
+      </c>
+      <c r="C71" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3">
+      <c r="A72" t="s">
+        <v>9</v>
+      </c>
+      <c r="B72" t="s">
+        <v>80</v>
+      </c>
+      <c r="C72" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3">
+      <c r="A73" t="s">
+        <v>9</v>
+      </c>
+      <c r="B73" t="s">
+        <v>81</v>
+      </c>
+      <c r="C73" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3">
+      <c r="A74" t="s">
+        <v>9</v>
+      </c>
+      <c r="B74" t="s">
+        <v>82</v>
+      </c>
+      <c r="C74" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3">
+      <c r="A75" t="s">
+        <v>9</v>
+      </c>
+      <c r="B75" t="s">
+        <v>83</v>
+      </c>
+      <c r="C75" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3">
+      <c r="A76" t="s">
+        <v>9</v>
+      </c>
+      <c r="B76" t="s">
+        <v>84</v>
+      </c>
+      <c r="C76" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3">
+      <c r="A77" t="s">
+        <v>9</v>
+      </c>
+      <c r="B77" t="s">
+        <v>85</v>
+      </c>
+      <c r="C77" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3">
+      <c r="A78" t="s">
+        <v>9</v>
+      </c>
+      <c r="B78" t="s">
+        <v>40</v>
+      </c>
+      <c r="C78" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3">
+      <c r="A79" t="s">
         <v>10</v>
       </c>
-      <c r="B9" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3">
-      <c r="A10" t="s">
+      <c r="B79" t="s">
+        <v>86</v>
+      </c>
+      <c r="C79" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3">
+      <c r="A80" t="s">
+        <v>10</v>
+      </c>
+      <c r="B80" t="s">
+        <v>76</v>
+      </c>
+      <c r="C80" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3">
+      <c r="A81" t="s">
+        <v>10</v>
+      </c>
+      <c r="B81" t="s">
+        <v>77</v>
+      </c>
+      <c r="C81" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3">
+      <c r="A82" t="s">
+        <v>10</v>
+      </c>
+      <c r="B82" t="s">
+        <v>78</v>
+      </c>
+      <c r="C82" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3">
+      <c r="A83" t="s">
+        <v>10</v>
+      </c>
+      <c r="B83" t="s">
+        <v>87</v>
+      </c>
+      <c r="C83" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3">
+      <c r="A84" t="s">
+        <v>10</v>
+      </c>
+      <c r="B84" t="s">
+        <v>88</v>
+      </c>
+      <c r="C84" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3">
+      <c r="A85" t="s">
+        <v>10</v>
+      </c>
+      <c r="B85" t="s">
+        <v>84</v>
+      </c>
+      <c r="C85" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3">
+      <c r="A86" t="s">
+        <v>10</v>
+      </c>
+      <c r="B86" t="s">
+        <v>40</v>
+      </c>
+      <c r="C86" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3">
+      <c r="A87" t="s">
+        <v>10</v>
+      </c>
+      <c r="B87" t="s">
+        <v>85</v>
+      </c>
+      <c r="C87" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3">
+      <c r="A88" t="s">
         <v>11</v>
       </c>
-      <c r="B10" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3">
-      <c r="A11" t="s">
+      <c r="B88" t="s">
+        <v>89</v>
+      </c>
+      <c r="C88" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3">
+      <c r="A89" t="s">
+        <v>11</v>
+      </c>
+      <c r="B89" t="s">
+        <v>82</v>
+      </c>
+      <c r="C89" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3">
+      <c r="A90" t="s">
+        <v>11</v>
+      </c>
+      <c r="B90" t="s">
+        <v>83</v>
+      </c>
+      <c r="C90" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3">
+      <c r="A91" t="s">
+        <v>11</v>
+      </c>
+      <c r="B91" t="s">
+        <v>90</v>
+      </c>
+      <c r="C91" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3">
+      <c r="A92" t="s">
+        <v>11</v>
+      </c>
+      <c r="B92" t="s">
+        <v>85</v>
+      </c>
+      <c r="C92" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3">
+      <c r="A93" t="s">
+        <v>11</v>
+      </c>
+      <c r="B93" t="s">
+        <v>91</v>
+      </c>
+      <c r="C93" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3">
+      <c r="A94" t="s">
+        <v>11</v>
+      </c>
+      <c r="B94" t="s">
+        <v>92</v>
+      </c>
+      <c r="C94" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3">
+      <c r="A95" t="s">
+        <v>11</v>
+      </c>
+      <c r="B95" t="s">
+        <v>84</v>
+      </c>
+      <c r="C95" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3">
+      <c r="A96" t="s">
         <v>12</v>
       </c>
-      <c r="B11" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3">
-      <c r="A12" t="s">
+      <c r="B96" t="s">
+        <v>93</v>
+      </c>
+      <c r="C96" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3">
+      <c r="A97" t="s">
+        <v>12</v>
+      </c>
+      <c r="B97" t="s">
+        <v>94</v>
+      </c>
+      <c r="C97" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3">
+      <c r="A98" t="s">
+        <v>12</v>
+      </c>
+      <c r="B98" t="s">
+        <v>95</v>
+      </c>
+      <c r="C98" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3">
+      <c r="A99" t="s">
+        <v>12</v>
+      </c>
+      <c r="B99" t="s">
+        <v>96</v>
+      </c>
+      <c r="C99" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3">
+      <c r="A100" t="s">
+        <v>12</v>
+      </c>
+      <c r="B100" t="s">
+        <v>97</v>
+      </c>
+      <c r="C100" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3">
+      <c r="A101" t="s">
+        <v>12</v>
+      </c>
+      <c r="B101" t="s">
+        <v>49</v>
+      </c>
+      <c r="C101" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3">
+      <c r="A102" t="s">
+        <v>12</v>
+      </c>
+      <c r="B102" t="s">
+        <v>38</v>
+      </c>
+      <c r="C102" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3">
+      <c r="A103" t="s">
+        <v>12</v>
+      </c>
+      <c r="B103" t="s">
+        <v>40</v>
+      </c>
+      <c r="C103" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3">
+      <c r="A104" t="s">
         <v>13</v>
       </c>
-      <c r="B12" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3">
-      <c r="A13" t="s">
+      <c r="B104" t="s">
+        <v>98</v>
+      </c>
+      <c r="C104" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3">
+      <c r="A105" t="s">
+        <v>13</v>
+      </c>
+      <c r="B105" t="s">
+        <v>99</v>
+      </c>
+      <c r="C105" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3">
+      <c r="A106" t="s">
+        <v>13</v>
+      </c>
+      <c r="B106" t="s">
+        <v>40</v>
+      </c>
+      <c r="C106" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3">
+      <c r="A107" t="s">
+        <v>13</v>
+      </c>
+      <c r="B107" t="s">
+        <v>63</v>
+      </c>
+      <c r="C107" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="108" spans="1:3">
+      <c r="A108" t="s">
+        <v>13</v>
+      </c>
+      <c r="B108" t="s">
+        <v>84</v>
+      </c>
+      <c r="C108" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3">
+      <c r="A109" t="s">
+        <v>13</v>
+      </c>
+      <c r="B109" t="s">
+        <v>89</v>
+      </c>
+      <c r="C109" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="110" spans="1:3">
+      <c r="A110" t="s">
         <v>14</v>
       </c>
-      <c r="B13" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3">
-      <c r="A14" t="s">
+      <c r="B110" t="s">
+        <v>100</v>
+      </c>
+      <c r="C110" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="111" spans="1:3">
+      <c r="A111" t="s">
+        <v>14</v>
+      </c>
+      <c r="B111" t="s">
+        <v>101</v>
+      </c>
+      <c r="C111" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="112" spans="1:3">
+      <c r="A112" t="s">
+        <v>14</v>
+      </c>
+      <c r="B112" t="s">
+        <v>102</v>
+      </c>
+      <c r="C112" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="113" spans="1:3">
+      <c r="A113" t="s">
+        <v>14</v>
+      </c>
+      <c r="B113" t="s">
+        <v>51</v>
+      </c>
+      <c r="C113" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="114" spans="1:3">
+      <c r="A114" t="s">
+        <v>14</v>
+      </c>
+      <c r="B114" t="s">
+        <v>49</v>
+      </c>
+      <c r="C114" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="115" spans="1:3">
+      <c r="A115" t="s">
+        <v>14</v>
+      </c>
+      <c r="B115" t="s">
+        <v>84</v>
+      </c>
+      <c r="C115" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="116" spans="1:3">
+      <c r="A116" t="s">
+        <v>14</v>
+      </c>
+      <c r="B116" t="s">
+        <v>40</v>
+      </c>
+      <c r="C116" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="117" spans="1:3">
+      <c r="A117" t="s">
         <v>15</v>
       </c>
-      <c r="B14" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3">
-      <c r="A15" t="s">
+      <c r="B117" t="s">
+        <v>103</v>
+      </c>
+      <c r="C117" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="118" spans="1:3">
+      <c r="A118" t="s">
+        <v>15</v>
+      </c>
+      <c r="B118" t="s">
+        <v>104</v>
+      </c>
+      <c r="C118" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="119" spans="1:3">
+      <c r="A119" t="s">
+        <v>15</v>
+      </c>
+      <c r="B119" t="s">
+        <v>105</v>
+      </c>
+      <c r="C119" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="120" spans="1:3">
+      <c r="A120" t="s">
+        <v>15</v>
+      </c>
+      <c r="B120" t="s">
+        <v>106</v>
+      </c>
+      <c r="C120" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="121" spans="1:3">
+      <c r="A121" t="s">
+        <v>15</v>
+      </c>
+      <c r="B121" t="s">
+        <v>107</v>
+      </c>
+      <c r="C121" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="122" spans="1:3">
+      <c r="A122" t="s">
+        <v>15</v>
+      </c>
+      <c r="B122" t="s">
+        <v>49</v>
+      </c>
+      <c r="C122" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="123" spans="1:3">
+      <c r="A123" t="s">
+        <v>15</v>
+      </c>
+      <c r="B123" t="s">
+        <v>48</v>
+      </c>
+      <c r="C123" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="124" spans="1:3">
+      <c r="A124" t="s">
+        <v>15</v>
+      </c>
+      <c r="B124" t="s">
+        <v>38</v>
+      </c>
+      <c r="C124" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="125" spans="1:3">
+      <c r="A125" t="s">
         <v>16</v>
       </c>
-      <c r="B15" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3">
-      <c r="A16" t="s">
+      <c r="B125" t="s">
+        <v>108</v>
+      </c>
+      <c r="C125" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="126" spans="1:3">
+      <c r="A126" t="s">
+        <v>16</v>
+      </c>
+      <c r="B126" t="s">
+        <v>109</v>
+      </c>
+      <c r="C126" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="127" spans="1:3">
+      <c r="A127" t="s">
+        <v>16</v>
+      </c>
+      <c r="B127" t="s">
+        <v>110</v>
+      </c>
+      <c r="C127" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="128" spans="1:3">
+      <c r="A128" t="s">
+        <v>16</v>
+      </c>
+      <c r="B128" t="s">
+        <v>111</v>
+      </c>
+      <c r="C128" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="129" spans="1:3">
+      <c r="A129" t="s">
+        <v>16</v>
+      </c>
+      <c r="B129" t="s">
+        <v>112</v>
+      </c>
+      <c r="C129" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="130" spans="1:3">
+      <c r="A130" t="s">
+        <v>16</v>
+      </c>
+      <c r="B130" t="s">
+        <v>113</v>
+      </c>
+      <c r="C130" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="131" spans="1:3">
+      <c r="A131" t="s">
+        <v>16</v>
+      </c>
+      <c r="B131" t="s">
+        <v>114</v>
+      </c>
+      <c r="C131" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="132" spans="1:3">
+      <c r="A132" t="s">
+        <v>16</v>
+      </c>
+      <c r="B132" t="s">
+        <v>115</v>
+      </c>
+      <c r="C132" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="133" spans="1:3">
+      <c r="A133" t="s">
+        <v>16</v>
+      </c>
+      <c r="B133" t="s">
+        <v>116</v>
+      </c>
+      <c r="C133" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="134" spans="1:3">
+      <c r="A134" t="s">
         <v>17</v>
       </c>
-      <c r="B16" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2">
-      <c r="A17" t="s">
-        <v>18</v>
-      </c>
-      <c r="B17" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2">
-      <c r="A18" t="s">
-        <v>19</v>
-      </c>
-      <c r="B18" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2">
-      <c r="A19" t="s">
-        <v>20</v>
-      </c>
-      <c r="B19" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2">
-      <c r="A20" t="s">
-        <v>21</v>
-      </c>
-      <c r="B20" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2">
-      <c r="A21" t="s">
-        <v>22</v>
-      </c>
-      <c r="B21" t="s">
-        <v>23</v>
+      <c r="B134" t="s">
+        <v>117</v>
+      </c>
+      <c r="C134" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="135" spans="1:3">
+      <c r="A135" t="s">
+        <v>17</v>
+      </c>
+      <c r="B135" t="s">
+        <v>118</v>
+      </c>
+      <c r="C135" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="136" spans="1:3">
+      <c r="A136" t="s">
+        <v>17</v>
+      </c>
+      <c r="B136" t="s">
+        <v>119</v>
+      </c>
+      <c r="C136" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="137" spans="1:3">
+      <c r="A137" t="s">
+        <v>17</v>
+      </c>
+      <c r="B137" t="s">
+        <v>120</v>
+      </c>
+      <c r="C137" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="138" spans="1:3">
+      <c r="A138" t="s">
+        <v>17</v>
+      </c>
+      <c r="B138" t="s">
+        <v>121</v>
+      </c>
+      <c r="C138" t="s">
+        <v>123</v>
       </c>
     </row>
   </sheetData>

--- a/clients/Poojamani/AY 2026-27/document_checklist.xlsx
+++ b/clients/Poojamani/AY 2026-27/document_checklist.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="415" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="463" uniqueCount="130">
   <si>
     <t>Category</t>
   </si>
@@ -70,6 +70,9 @@
     <t>Final Audit Review Data</t>
   </si>
   <si>
+    <t>Balance Sheet Supporting Data</t>
+  </si>
+  <si>
     <t>Bank Statements</t>
   </si>
   <si>
@@ -380,6 +383,21 @@
   </si>
   <si>
     <t>Tax_Report_Linkage</t>
+  </si>
+  <si>
+    <t>Income_Ledgers</t>
+  </si>
+  <si>
+    <t>Journal_Register</t>
+  </si>
+  <si>
+    <t>Debtor_Ageing</t>
+  </si>
+  <si>
+    <t>Outstanding_Receivables</t>
+  </si>
+  <si>
+    <t>Capital_Account</t>
   </si>
   <si>
     <t>Received</t>
@@ -717,7 +735,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D138"/>
+  <dimension ref="A1:D154"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -739,10 +757,10 @@
         <v>4</v>
       </c>
       <c r="B2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C2" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -750,10 +768,10 @@
         <v>4</v>
       </c>
       <c r="B3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C3" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -761,10 +779,10 @@
         <v>4</v>
       </c>
       <c r="B4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C4" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -772,10 +790,10 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C5" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -783,10 +801,10 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C6" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -794,10 +812,10 @@
         <v>4</v>
       </c>
       <c r="B7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C7" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -805,10 +823,10 @@
         <v>4</v>
       </c>
       <c r="B8" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C8" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -816,10 +834,10 @@
         <v>4</v>
       </c>
       <c r="B9" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C9" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -827,10 +845,10 @@
         <v>4</v>
       </c>
       <c r="B10" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C10" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -838,10 +856,10 @@
         <v>4</v>
       </c>
       <c r="B11" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C11" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -849,10 +867,10 @@
         <v>4</v>
       </c>
       <c r="B12" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C12" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -860,10 +878,10 @@
         <v>4</v>
       </c>
       <c r="B13" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C13" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -871,10 +889,10 @@
         <v>4</v>
       </c>
       <c r="B14" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C14" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -882,10 +900,10 @@
         <v>4</v>
       </c>
       <c r="B15" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C15" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -893,10 +911,10 @@
         <v>4</v>
       </c>
       <c r="B16" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C16" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -904,10 +922,10 @@
         <v>4</v>
       </c>
       <c r="B17" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C17" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -915,10 +933,10 @@
         <v>4</v>
       </c>
       <c r="B18" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C18" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -926,10 +944,10 @@
         <v>4</v>
       </c>
       <c r="B19" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C19" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -937,10 +955,10 @@
         <v>4</v>
       </c>
       <c r="B20" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C20" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -948,10 +966,10 @@
         <v>4</v>
       </c>
       <c r="B21" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C21" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -959,10 +977,10 @@
         <v>5</v>
       </c>
       <c r="B22" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C22" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -970,10 +988,10 @@
         <v>5</v>
       </c>
       <c r="B23" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C23" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -981,10 +999,10 @@
         <v>5</v>
       </c>
       <c r="B24" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C24" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -992,10 +1010,10 @@
         <v>5</v>
       </c>
       <c r="B25" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C25" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -1003,10 +1021,10 @@
         <v>5</v>
       </c>
       <c r="B26" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C26" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -1014,10 +1032,10 @@
         <v>5</v>
       </c>
       <c r="B27" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C27" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
     </row>
     <row r="28" spans="1:3">
@@ -1025,10 +1043,10 @@
         <v>5</v>
       </c>
       <c r="B28" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C28" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -1036,10 +1054,10 @@
         <v>5</v>
       </c>
       <c r="B29" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C29" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
     </row>
     <row r="30" spans="1:3">
@@ -1047,10 +1065,10 @@
         <v>6</v>
       </c>
       <c r="B30" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C30" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
     </row>
     <row r="31" spans="1:3">
@@ -1058,10 +1076,10 @@
         <v>6</v>
       </c>
       <c r="B31" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C31" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
     </row>
     <row r="32" spans="1:3">
@@ -1069,10 +1087,10 @@
         <v>6</v>
       </c>
       <c r="B32" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C32" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
     </row>
     <row r="33" spans="1:3">
@@ -1080,10 +1098,10 @@
         <v>6</v>
       </c>
       <c r="B33" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C33" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
     </row>
     <row r="34" spans="1:3">
@@ -1091,10 +1109,10 @@
         <v>6</v>
       </c>
       <c r="B34" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C34" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
     </row>
     <row r="35" spans="1:3">
@@ -1102,10 +1120,10 @@
         <v>6</v>
       </c>
       <c r="B35" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C35" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
     </row>
     <row r="36" spans="1:3">
@@ -1113,10 +1131,10 @@
         <v>7</v>
       </c>
       <c r="B36" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C36" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
     </row>
     <row r="37" spans="1:3">
@@ -1124,10 +1142,10 @@
         <v>7</v>
       </c>
       <c r="B37" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C37" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
     </row>
     <row r="38" spans="1:3">
@@ -1135,10 +1153,10 @@
         <v>7</v>
       </c>
       <c r="B38" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C38" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
     </row>
     <row r="39" spans="1:3">
@@ -1146,10 +1164,10 @@
         <v>7</v>
       </c>
       <c r="B39" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C39" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
     </row>
     <row r="40" spans="1:3">
@@ -1157,10 +1175,10 @@
         <v>7</v>
       </c>
       <c r="B40" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C40" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
     </row>
     <row r="41" spans="1:3">
@@ -1168,10 +1186,10 @@
         <v>7</v>
       </c>
       <c r="B41" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C41" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
     </row>
     <row r="42" spans="1:3">
@@ -1179,10 +1197,10 @@
         <v>7</v>
       </c>
       <c r="B42" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C42" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
     </row>
     <row r="43" spans="1:3">
@@ -1190,10 +1208,10 @@
         <v>7</v>
       </c>
       <c r="B43" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C43" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
     </row>
     <row r="44" spans="1:3">
@@ -1201,10 +1219,10 @@
         <v>7</v>
       </c>
       <c r="B44" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C44" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
     </row>
     <row r="45" spans="1:3">
@@ -1212,10 +1230,10 @@
         <v>7</v>
       </c>
       <c r="B45" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C45" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
     </row>
     <row r="46" spans="1:3">
@@ -1223,10 +1241,10 @@
         <v>7</v>
       </c>
       <c r="B46" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C46" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
     </row>
     <row r="47" spans="1:3">
@@ -1234,10 +1252,10 @@
         <v>8</v>
       </c>
       <c r="B47" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C47" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
     </row>
     <row r="48" spans="1:3">
@@ -1245,10 +1263,10 @@
         <v>8</v>
       </c>
       <c r="B48" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C48" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
     </row>
     <row r="49" spans="1:3">
@@ -1256,10 +1274,10 @@
         <v>8</v>
       </c>
       <c r="B49" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C49" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
     </row>
     <row r="50" spans="1:3">
@@ -1267,10 +1285,10 @@
         <v>8</v>
       </c>
       <c r="B50" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C50" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
     </row>
     <row r="51" spans="1:3">
@@ -1278,10 +1296,10 @@
         <v>8</v>
       </c>
       <c r="B51" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C51" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
     </row>
     <row r="52" spans="1:3">
@@ -1289,10 +1307,10 @@
         <v>8</v>
       </c>
       <c r="B52" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C52" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
     </row>
     <row r="53" spans="1:3">
@@ -1300,10 +1318,10 @@
         <v>8</v>
       </c>
       <c r="B53" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C53" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
     </row>
     <row r="54" spans="1:3">
@@ -1311,10 +1329,10 @@
         <v>8</v>
       </c>
       <c r="B54" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C54" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
     </row>
     <row r="55" spans="1:3">
@@ -1322,10 +1340,10 @@
         <v>8</v>
       </c>
       <c r="B55" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C55" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
     </row>
     <row r="56" spans="1:3">
@@ -1333,10 +1351,10 @@
         <v>8</v>
       </c>
       <c r="B56" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C56" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
     </row>
     <row r="57" spans="1:3">
@@ -1344,10 +1362,10 @@
         <v>8</v>
       </c>
       <c r="B57" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C57" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
     </row>
     <row r="58" spans="1:3">
@@ -1355,10 +1373,10 @@
         <v>8</v>
       </c>
       <c r="B58" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C58" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
     </row>
     <row r="59" spans="1:3">
@@ -1366,10 +1384,10 @@
         <v>9</v>
       </c>
       <c r="B59" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C59" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
     </row>
     <row r="60" spans="1:3">
@@ -1377,10 +1395,10 @@
         <v>9</v>
       </c>
       <c r="B60" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C60" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
     </row>
     <row r="61" spans="1:3">
@@ -1388,10 +1406,10 @@
         <v>9</v>
       </c>
       <c r="B61" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C61" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
     </row>
     <row r="62" spans="1:3">
@@ -1399,10 +1417,10 @@
         <v>9</v>
       </c>
       <c r="B62" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C62" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
     </row>
     <row r="63" spans="1:3">
@@ -1410,10 +1428,10 @@
         <v>9</v>
       </c>
       <c r="B63" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C63" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
     </row>
     <row r="64" spans="1:3">
@@ -1421,10 +1439,10 @@
         <v>9</v>
       </c>
       <c r="B64" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C64" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
     </row>
     <row r="65" spans="1:3">
@@ -1432,10 +1450,10 @@
         <v>9</v>
       </c>
       <c r="B65" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C65" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
     </row>
     <row r="66" spans="1:3">
@@ -1443,10 +1461,10 @@
         <v>9</v>
       </c>
       <c r="B66" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C66" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
     </row>
     <row r="67" spans="1:3">
@@ -1454,10 +1472,10 @@
         <v>9</v>
       </c>
       <c r="B67" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C67" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
     </row>
     <row r="68" spans="1:3">
@@ -1465,10 +1483,10 @@
         <v>9</v>
       </c>
       <c r="B68" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C68" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
     </row>
     <row r="69" spans="1:3">
@@ -1476,10 +1494,10 @@
         <v>9</v>
       </c>
       <c r="B69" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C69" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
     </row>
     <row r="70" spans="1:3">
@@ -1487,10 +1505,10 @@
         <v>9</v>
       </c>
       <c r="B70" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C70" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
     </row>
     <row r="71" spans="1:3">
@@ -1498,10 +1516,10 @@
         <v>9</v>
       </c>
       <c r="B71" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C71" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
     </row>
     <row r="72" spans="1:3">
@@ -1509,10 +1527,10 @@
         <v>9</v>
       </c>
       <c r="B72" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C72" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
     </row>
     <row r="73" spans="1:3">
@@ -1520,10 +1538,10 @@
         <v>9</v>
       </c>
       <c r="B73" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C73" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
     </row>
     <row r="74" spans="1:3">
@@ -1531,10 +1549,10 @@
         <v>9</v>
       </c>
       <c r="B74" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C74" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
     </row>
     <row r="75" spans="1:3">
@@ -1542,10 +1560,10 @@
         <v>9</v>
       </c>
       <c r="B75" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C75" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
     </row>
     <row r="76" spans="1:3">
@@ -1553,10 +1571,10 @@
         <v>9</v>
       </c>
       <c r="B76" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C76" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
     </row>
     <row r="77" spans="1:3">
@@ -1564,10 +1582,10 @@
         <v>9</v>
       </c>
       <c r="B77" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C77" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
     </row>
     <row r="78" spans="1:3">
@@ -1575,10 +1593,10 @@
         <v>9</v>
       </c>
       <c r="B78" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C78" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
     </row>
     <row r="79" spans="1:3">
@@ -1586,10 +1604,10 @@
         <v>10</v>
       </c>
       <c r="B79" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C79" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
     </row>
     <row r="80" spans="1:3">
@@ -1597,10 +1615,10 @@
         <v>10</v>
       </c>
       <c r="B80" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C80" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
     </row>
     <row r="81" spans="1:3">
@@ -1608,10 +1626,10 @@
         <v>10</v>
       </c>
       <c r="B81" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C81" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
     </row>
     <row r="82" spans="1:3">
@@ -1619,10 +1637,10 @@
         <v>10</v>
       </c>
       <c r="B82" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C82" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
     </row>
     <row r="83" spans="1:3">
@@ -1630,10 +1648,10 @@
         <v>10</v>
       </c>
       <c r="B83" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C83" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
     </row>
     <row r="84" spans="1:3">
@@ -1641,10 +1659,10 @@
         <v>10</v>
       </c>
       <c r="B84" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C84" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
     </row>
     <row r="85" spans="1:3">
@@ -1652,10 +1670,10 @@
         <v>10</v>
       </c>
       <c r="B85" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C85" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
     </row>
     <row r="86" spans="1:3">
@@ -1663,10 +1681,10 @@
         <v>10</v>
       </c>
       <c r="B86" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C86" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
     </row>
     <row r="87" spans="1:3">
@@ -1674,10 +1692,10 @@
         <v>10</v>
       </c>
       <c r="B87" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C87" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
     </row>
     <row r="88" spans="1:3">
@@ -1685,10 +1703,10 @@
         <v>11</v>
       </c>
       <c r="B88" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C88" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
     </row>
     <row r="89" spans="1:3">
@@ -1696,10 +1714,10 @@
         <v>11</v>
       </c>
       <c r="B89" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C89" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
     </row>
     <row r="90" spans="1:3">
@@ -1707,10 +1725,10 @@
         <v>11</v>
       </c>
       <c r="B90" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C90" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
     </row>
     <row r="91" spans="1:3">
@@ -1718,10 +1736,10 @@
         <v>11</v>
       </c>
       <c r="B91" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C91" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
     </row>
     <row r="92" spans="1:3">
@@ -1729,10 +1747,10 @@
         <v>11</v>
       </c>
       <c r="B92" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C92" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
     </row>
     <row r="93" spans="1:3">
@@ -1740,10 +1758,10 @@
         <v>11</v>
       </c>
       <c r="B93" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C93" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
     </row>
     <row r="94" spans="1:3">
@@ -1751,10 +1769,10 @@
         <v>11</v>
       </c>
       <c r="B94" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C94" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
     </row>
     <row r="95" spans="1:3">
@@ -1762,10 +1780,10 @@
         <v>11</v>
       </c>
       <c r="B95" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C95" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
     </row>
     <row r="96" spans="1:3">
@@ -1773,10 +1791,10 @@
         <v>12</v>
       </c>
       <c r="B96" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C96" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
     </row>
     <row r="97" spans="1:3">
@@ -1784,10 +1802,10 @@
         <v>12</v>
       </c>
       <c r="B97" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C97" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
     </row>
     <row r="98" spans="1:3">
@@ -1795,10 +1813,10 @@
         <v>12</v>
       </c>
       <c r="B98" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C98" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
     </row>
     <row r="99" spans="1:3">
@@ -1806,10 +1824,10 @@
         <v>12</v>
       </c>
       <c r="B99" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C99" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
     </row>
     <row r="100" spans="1:3">
@@ -1817,10 +1835,10 @@
         <v>12</v>
       </c>
       <c r="B100" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C100" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
     </row>
     <row r="101" spans="1:3">
@@ -1828,10 +1846,10 @@
         <v>12</v>
       </c>
       <c r="B101" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C101" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
     </row>
     <row r="102" spans="1:3">
@@ -1839,10 +1857,10 @@
         <v>12</v>
       </c>
       <c r="B102" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C102" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
     </row>
     <row r="103" spans="1:3">
@@ -1850,10 +1868,10 @@
         <v>12</v>
       </c>
       <c r="B103" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C103" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
     </row>
     <row r="104" spans="1:3">
@@ -1861,10 +1879,10 @@
         <v>13</v>
       </c>
       <c r="B104" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C104" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
     </row>
     <row r="105" spans="1:3">
@@ -1872,10 +1890,10 @@
         <v>13</v>
       </c>
       <c r="B105" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C105" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
     </row>
     <row r="106" spans="1:3">
@@ -1883,10 +1901,10 @@
         <v>13</v>
       </c>
       <c r="B106" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C106" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
     </row>
     <row r="107" spans="1:3">
@@ -1894,10 +1912,10 @@
         <v>13</v>
       </c>
       <c r="B107" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C107" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
     </row>
     <row r="108" spans="1:3">
@@ -1905,10 +1923,10 @@
         <v>13</v>
       </c>
       <c r="B108" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C108" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
     </row>
     <row r="109" spans="1:3">
@@ -1916,10 +1934,10 @@
         <v>13</v>
       </c>
       <c r="B109" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C109" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
     </row>
     <row r="110" spans="1:3">
@@ -1927,10 +1945,10 @@
         <v>14</v>
       </c>
       <c r="B110" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C110" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
     </row>
     <row r="111" spans="1:3">
@@ -1938,10 +1956,10 @@
         <v>14</v>
       </c>
       <c r="B111" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C111" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
     </row>
     <row r="112" spans="1:3">
@@ -1949,10 +1967,10 @@
         <v>14</v>
       </c>
       <c r="B112" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C112" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
     </row>
     <row r="113" spans="1:3">
@@ -1960,10 +1978,10 @@
         <v>14</v>
       </c>
       <c r="B113" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C113" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
     </row>
     <row r="114" spans="1:3">
@@ -1971,10 +1989,10 @@
         <v>14</v>
       </c>
       <c r="B114" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C114" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
     </row>
     <row r="115" spans="1:3">
@@ -1982,10 +2000,10 @@
         <v>14</v>
       </c>
       <c r="B115" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C115" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
     </row>
     <row r="116" spans="1:3">
@@ -1993,10 +2011,10 @@
         <v>14</v>
       </c>
       <c r="B116" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C116" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
     </row>
     <row r="117" spans="1:3">
@@ -2004,10 +2022,10 @@
         <v>15</v>
       </c>
       <c r="B117" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C117" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
     </row>
     <row r="118" spans="1:3">
@@ -2015,10 +2033,10 @@
         <v>15</v>
       </c>
       <c r="B118" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C118" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
     </row>
     <row r="119" spans="1:3">
@@ -2026,10 +2044,10 @@
         <v>15</v>
       </c>
       <c r="B119" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C119" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
     </row>
     <row r="120" spans="1:3">
@@ -2037,10 +2055,10 @@
         <v>15</v>
       </c>
       <c r="B120" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C120" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
     </row>
     <row r="121" spans="1:3">
@@ -2048,10 +2066,10 @@
         <v>15</v>
       </c>
       <c r="B121" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C121" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
     </row>
     <row r="122" spans="1:3">
@@ -2059,10 +2077,10 @@
         <v>15</v>
       </c>
       <c r="B122" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C122" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
     </row>
     <row r="123" spans="1:3">
@@ -2070,10 +2088,10 @@
         <v>15</v>
       </c>
       <c r="B123" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C123" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
     </row>
     <row r="124" spans="1:3">
@@ -2081,10 +2099,10 @@
         <v>15</v>
       </c>
       <c r="B124" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C124" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
     </row>
     <row r="125" spans="1:3">
@@ -2092,10 +2110,10 @@
         <v>16</v>
       </c>
       <c r="B125" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C125" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
     </row>
     <row r="126" spans="1:3">
@@ -2103,10 +2121,10 @@
         <v>16</v>
       </c>
       <c r="B126" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C126" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
     </row>
     <row r="127" spans="1:3">
@@ -2114,10 +2132,10 @@
         <v>16</v>
       </c>
       <c r="B127" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C127" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
     </row>
     <row r="128" spans="1:3">
@@ -2125,10 +2143,10 @@
         <v>16</v>
       </c>
       <c r="B128" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C128" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
     </row>
     <row r="129" spans="1:3">
@@ -2136,10 +2154,10 @@
         <v>16</v>
       </c>
       <c r="B129" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C129" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
     </row>
     <row r="130" spans="1:3">
@@ -2147,10 +2165,10 @@
         <v>16</v>
       </c>
       <c r="B130" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C130" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
     </row>
     <row r="131" spans="1:3">
@@ -2158,10 +2176,10 @@
         <v>16</v>
       </c>
       <c r="B131" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C131" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
     </row>
     <row r="132" spans="1:3">
@@ -2169,10 +2187,10 @@
         <v>16</v>
       </c>
       <c r="B132" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C132" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
     </row>
     <row r="133" spans="1:3">
@@ -2180,10 +2198,10 @@
         <v>16</v>
       </c>
       <c r="B133" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C133" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
     </row>
     <row r="134" spans="1:3">
@@ -2191,10 +2209,10 @@
         <v>17</v>
       </c>
       <c r="B134" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C134" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
     </row>
     <row r="135" spans="1:3">
@@ -2202,10 +2220,10 @@
         <v>17</v>
       </c>
       <c r="B135" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C135" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
     </row>
     <row r="136" spans="1:3">
@@ -2213,10 +2231,10 @@
         <v>17</v>
       </c>
       <c r="B136" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C136" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
     </row>
     <row r="137" spans="1:3">
@@ -2224,10 +2242,10 @@
         <v>17</v>
       </c>
       <c r="B137" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C137" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
     </row>
     <row r="138" spans="1:3">
@@ -2235,10 +2253,186 @@
         <v>17</v>
       </c>
       <c r="B138" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C138" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="139" spans="1:3">
+      <c r="A139" t="s">
+        <v>5</v>
+      </c>
+      <c r="B139" t="s">
         <v>123</v>
+      </c>
+      <c r="C139" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="140" spans="1:3">
+      <c r="A140" t="s">
+        <v>5</v>
+      </c>
+      <c r="B140" t="s">
+        <v>64</v>
+      </c>
+      <c r="C140" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="141" spans="1:3">
+      <c r="A141" t="s">
+        <v>5</v>
+      </c>
+      <c r="B141" t="s">
+        <v>124</v>
+      </c>
+      <c r="C141" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="142" spans="1:3">
+      <c r="A142" t="s">
+        <v>8</v>
+      </c>
+      <c r="B142" t="s">
+        <v>52</v>
+      </c>
+      <c r="C142" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="143" spans="1:3">
+      <c r="A143" t="s">
+        <v>8</v>
+      </c>
+      <c r="B143" t="s">
+        <v>51</v>
+      </c>
+      <c r="C143" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="144" spans="1:3">
+      <c r="A144" t="s">
+        <v>8</v>
+      </c>
+      <c r="B144" t="s">
+        <v>85</v>
+      </c>
+      <c r="C144" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="145" spans="1:3">
+      <c r="A145" t="s">
+        <v>8</v>
+      </c>
+      <c r="B145" t="s">
+        <v>93</v>
+      </c>
+      <c r="C145" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="146" spans="1:3">
+      <c r="A146" t="s">
+        <v>8</v>
+      </c>
+      <c r="B146" t="s">
+        <v>87</v>
+      </c>
+      <c r="C146" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="147" spans="1:3">
+      <c r="A147" t="s">
+        <v>18</v>
+      </c>
+      <c r="B147" t="s">
+        <v>125</v>
+      </c>
+      <c r="C147" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="148" spans="1:3">
+      <c r="A148" t="s">
+        <v>18</v>
+      </c>
+      <c r="B148" t="s">
+        <v>102</v>
+      </c>
+      <c r="C148" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="149" spans="1:3">
+      <c r="A149" t="s">
+        <v>18</v>
+      </c>
+      <c r="B149" t="s">
+        <v>126</v>
+      </c>
+      <c r="C149" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="150" spans="1:3">
+      <c r="A150" t="s">
+        <v>18</v>
+      </c>
+      <c r="B150" t="s">
+        <v>103</v>
+      </c>
+      <c r="C150" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="151" spans="1:3">
+      <c r="A151" t="s">
+        <v>18</v>
+      </c>
+      <c r="B151" t="s">
+        <v>127</v>
+      </c>
+      <c r="C151" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="152" spans="1:3">
+      <c r="A152" t="s">
+        <v>18</v>
+      </c>
+      <c r="B152" t="s">
+        <v>90</v>
+      </c>
+      <c r="C152" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="153" spans="1:3">
+      <c r="A153" t="s">
+        <v>18</v>
+      </c>
+      <c r="B153" t="s">
+        <v>94</v>
+      </c>
+      <c r="C153" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="154" spans="1:3">
+      <c r="A154" t="s">
+        <v>18</v>
+      </c>
+      <c r="B154" t="s">
+        <v>76</v>
+      </c>
+      <c r="C154" t="s">
+        <v>129</v>
       </c>
     </row>
   </sheetData>
